--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,10 +119,6 @@
   <si>
     <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -723,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1056,6 +1052,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1065,7 +1064,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1397,6 +1396,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1440,7 +1442,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1773,6 +1775,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1782,7 +1787,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2111,6 +2116,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2154,7 +2162,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2487,6 +2495,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2496,7 +2507,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2828,6 +2839,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2850,11 +2864,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="94116864"/>
-        <c:axId val="99717888"/>
+        <c:axId val="346047232"/>
+        <c:axId val="351267072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="94116864"/>
+        <c:axId val="346047232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2897,14 +2911,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99717888"/>
+        <c:crossAx val="351267072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99717888"/>
+        <c:axId val="351267072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2953,7 +2967,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94116864"/>
+        <c:crossAx val="346047232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3166,7 +3180,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3463,6 +3477,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3472,7 +3489,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3769,6 +3786,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>6917.0073080000038</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7143.8348660000038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3811,7 +3831,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4108,6 +4128,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4117,7 +4140,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4414,6 +4437,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>9673.0994388317722</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>9898.842556077434</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4456,7 +4482,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4753,6 +4779,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4762,7 +4791,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5059,6 +5088,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2755.0076900774302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5080,11 +5112,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="390303104"/>
-        <c:axId val="399529088"/>
+        <c:axId val="465297408"/>
+        <c:axId val="465299712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="390303104"/>
+        <c:axId val="465297408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5127,14 +5159,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399529088"/>
+        <c:crossAx val="465299712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399529088"/>
+        <c:axId val="465299712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5183,7 +5215,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390303104"/>
+        <c:crossAx val="465297408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5291,7 +5323,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5334,7 +5366,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5647,7 +5679,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10331,6 +10363,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B115" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.1747980992467859</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I115" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J115" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K115" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10347,7 +10414,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10438,7 +10505,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -14486,6 +14553,41 @@
         <v>2756.0921308317684</v>
       </c>
       <c r="K102" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>226.82755800000027</v>
+      </c>
+      <c r="E103" s="22">
+        <v>131.63693859430239</v>
+      </c>
+      <c r="F103" s="22">
+        <v>141.49549090646764</v>
+      </c>
+      <c r="G103" s="22">
+        <v>243.81512524566159</v>
+      </c>
+      <c r="H103" s="22">
+        <v>7143.8348660000038</v>
+      </c>
+      <c r="I103" s="22">
+        <v>9898.842556077434</v>
+      </c>
+      <c r="J103" s="22">
+        <v>2755.0076900774302</v>
+      </c>
+      <c r="K103" s="21">
         <v>9655.027430831773</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -719,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1055,6 +1055,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1064,7 +1067,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1399,6 +1402,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1442,7 +1448,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1778,6 +1784,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1787,7 +1796,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2119,6 +2128,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2162,7 +2174,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2498,6 +2510,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2507,7 +2522,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2842,6 +2857,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2864,11 +2882,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="346047232"/>
-        <c:axId val="351267072"/>
+        <c:axId val="678416384"/>
+        <c:axId val="678418304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="346047232"/>
+        <c:axId val="678416384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2911,14 +2929,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="351267072"/>
+        <c:crossAx val="678418304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="351267072"/>
+        <c:axId val="678418304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2967,7 +2985,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346047232"/>
+        <c:crossAx val="678416384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3180,7 +3198,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3480,6 +3498,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3489,7 +3510,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3789,6 +3810,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>7143.8348660000038</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7502.8270800000037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3831,7 +3855,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4131,6 +4155,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4140,7 +4167,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4440,6 +4467,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>9898.842556077434</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10245.792088846385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4482,7 +4512,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4782,6 +4812,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4791,7 +4824,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5091,6 +5124,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>2755.0076900774302</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2742.9650088463814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5112,11 +5148,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465297408"/>
-        <c:axId val="465299712"/>
+        <c:axId val="92100864"/>
+        <c:axId val="92102656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465297408"/>
+        <c:axId val="92100864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5159,14 +5195,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465299712"/>
+        <c:crossAx val="92102656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465299712"/>
+        <c:axId val="92102656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5215,7 +5251,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465297408"/>
+        <c:crossAx val="92100864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5323,7 +5359,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5366,7 +5402,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5679,7 +5715,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10398,6 +10434,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B116" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.1794961447368402</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I116" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J116" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K116" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10414,7 +10485,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14591,6 +14662,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>358.99221399999948</v>
+      </c>
+      <c r="E104" s="22">
+        <v>219.16228983773058</v>
+      </c>
+      <c r="F104" s="22">
+        <v>360.65778074419825</v>
+      </c>
+      <c r="G104" s="22">
+        <v>590.76465801461165</v>
+      </c>
+      <c r="H104" s="22">
+        <v>7502.8270800000037</v>
+      </c>
+      <c r="I104" s="22">
+        <v>10245.792088846385</v>
+      </c>
+      <c r="J104" s="22">
+        <v>2742.9650088463814</v>
+      </c>
+      <c r="K104" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -719,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1058,6 +1058,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1067,7 +1070,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1405,6 +1408,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1448,7 +1454,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1787,6 +1793,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1796,7 +1805,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2131,6 +2140,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2174,7 +2186,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2513,6 +2525,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2522,7 +2537,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2860,6 +2875,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2882,11 +2900,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="678416384"/>
-        <c:axId val="678418304"/>
+        <c:axId val="387867776"/>
+        <c:axId val="387869312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="678416384"/>
+        <c:axId val="387867776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2929,14 +2947,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678418304"/>
+        <c:crossAx val="387869312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="678418304"/>
+        <c:axId val="387869312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2985,7 +3003,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678416384"/>
+        <c:crossAx val="387867776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3198,7 +3216,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3501,6 +3519,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3510,7 +3531,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3813,6 +3834,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>7502.8270800000037</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7669.4991380000019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3855,7 +3879,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4158,6 +4182,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4167,7 +4194,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4470,6 +4497,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>10245.792088846385</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>10455.815212091835</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4512,7 +4542,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4815,6 +4845,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4824,7 +4857,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5127,6 +5160,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>2742.9650088463814</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>2786.3160740918329</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5148,11 +5184,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92100864"/>
-        <c:axId val="92102656"/>
+        <c:axId val="489279488"/>
+        <c:axId val="489281024"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92100864"/>
+        <c:axId val="489279488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5195,14 +5231,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92102656"/>
+        <c:crossAx val="489281024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92102656"/>
+        <c:axId val="489281024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5251,7 +5287,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92100864"/>
+        <c:crossAx val="489279488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5359,7 +5395,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5402,7 +5438,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5715,7 +5751,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF116"/>
+  <dimension ref="A1:AF117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10469,6 +10505,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="117" spans="1:11" ht="12.75">
+      <c r="A117" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B117" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C117" s="20">
+        <v>1.1845099478487591</v>
+      </c>
+      <c r="D117" s="21">
+        <v>0</v>
+      </c>
+      <c r="E117" s="22">
+        <v>0</v>
+      </c>
+      <c r="F117" s="22">
+        <v>0</v>
+      </c>
+      <c r="G117" s="22">
+        <v>0</v>
+      </c>
+      <c r="H117" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I117" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J117" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K117" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10485,7 +10556,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14697,6 +14768,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>166.67205799999851</v>
+      </c>
+      <c r="E105" s="22">
+        <v>94.795906086836979</v>
+      </c>
+      <c r="F105" s="22">
+        <v>455.45368683103521</v>
+      </c>
+      <c r="G105" s="22">
+        <v>800.78778126006273</v>
+      </c>
+      <c r="H105" s="22">
+        <v>7669.4991380000019</v>
+      </c>
+      <c r="I105" s="22">
+        <v>10455.815212091835</v>
+      </c>
+      <c r="J105" s="22">
+        <v>2786.3160740918329</v>
+      </c>
+      <c r="K105" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
